--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.43885991514382</v>
+        <v>9.008814736210871</v>
       </c>
       <c r="D2" t="n">
-        <v>55.58661602110958</v>
+        <v>9.032825103430307</v>
       </c>
       <c r="E2" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F2" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>83.18805842643307</v>
+        <v>13.51805949429538</v>
       </c>
       <c r="D3" t="n">
-        <v>82.75037102866135</v>
+        <v>13.44693529215747</v>
       </c>
       <c r="E3" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F3" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.30691878892096</v>
+        <v>8.499874303199656</v>
       </c>
       <c r="D4" t="n">
-        <v>52.24579619676651</v>
+        <v>8.489941881974557</v>
       </c>
       <c r="E4" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F4" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.17268562674863</v>
+        <v>9.290561414346653</v>
       </c>
       <c r="D5" t="n">
-        <v>56.86130527134808</v>
+        <v>9.239962106594064</v>
       </c>
       <c r="E5" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F5" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.43474055310428</v>
+        <v>3.483145339879446</v>
       </c>
       <c r="D6" t="n">
-        <v>21.87228019330809</v>
+        <v>3.554245531412565</v>
       </c>
       <c r="E6" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F6" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.39153642653637</v>
+        <v>5.588624669312161</v>
       </c>
       <c r="D7" t="n">
-        <v>39.14715826212677</v>
+        <v>6.3614132175956</v>
       </c>
       <c r="E7" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F7" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.83427019635081</v>
+        <v>6.310568906907006</v>
       </c>
       <c r="D8" t="n">
-        <v>44.33872326492543</v>
+        <v>7.205042530550383</v>
       </c>
       <c r="E8" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F8" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.64717874889513</v>
+        <v>4.167666546695458</v>
       </c>
       <c r="D9" t="n">
-        <v>30.99193443462347</v>
+        <v>5.036189345626314</v>
       </c>
       <c r="E9" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F9" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.10410600575697</v>
+        <v>2.454417225935507</v>
       </c>
       <c r="D10" t="n">
-        <v>10.02464107407257</v>
+        <v>1.629004174536792</v>
       </c>
       <c r="E10" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F10" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.16693311863822</v>
+        <v>3.764626631778711</v>
       </c>
       <c r="D11" t="n">
-        <v>20.72441299740187</v>
+        <v>3.367717112077804</v>
       </c>
       <c r="E11" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F11" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.28554666352181</v>
+        <v>2.808901332822295</v>
       </c>
       <c r="D12" t="n">
-        <v>18.63214157020832</v>
+        <v>3.027723005158852</v>
       </c>
       <c r="E12" t="n">
-        <v>20.29142387732674</v>
+        <v>3.297356380065596</v>
       </c>
       <c r="F12" t="n">
-        <v>20.57477036611499</v>
+        <v>3.343400184493686</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
